--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-bf.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-bf.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4860" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4884" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02</t>
+    <t>2026-09-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -264,7 +264,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}vs-de-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-de-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
   </si>
   <si>
     <t>Observation.id</t>
@@ -292,6 +292,14 @@
     <t>Resource.id</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>Observation.meta</t>
   </si>
   <si>
@@ -308,10 +316,6 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>Observation.meta.id</t>
   </si>
   <si>
@@ -637,7 +641,14 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.exists() implies (reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids')) or (reference='#' and %rootResource!=%resource))}</t>
   </si>
   <si>
     <t>Observation.partOf</t>
@@ -824,6 +835,9 @@
     <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
@@ -1095,8 +1109,8 @@
     <t>closed</t>
   </si>
   <si>
-    <t xml:space="preserve">obs-7
-</t>
+    <t>ele-1
+obs-7</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity</t>
@@ -1211,6 +1225,9 @@
     <t>The identification of the system that provides the coded form of the unit.</t>
   </si>
   <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
+  </si>
+  <si>
     <t>Need to know the system that defines the coded form of the unit.</t>
   </si>
   <si>
@@ -1220,8 +1237,8 @@
     <t>Quantity.system</t>
   </si>
   <si>
-    <t xml:space="preserve">qty-3
-</t>
+    <t>ele-1
+qty-3</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.code</t>
@@ -1270,8 +1287,8 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
-    <t xml:space="preserve">obs-6
-</t>
+    <t>ele-1
+obs-6</t>
   </si>
   <si>
     <t>Observation.interpretation</t>
@@ -1449,8 +1466,15 @@
     <t>untere Normgrenze</t>
   </si>
   <si>
-    <t xml:space="preserve">obs-3
-</t>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1
+obs-3</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>Observation.referenceRange.high</t>
@@ -1517,7 +1541,14 @@
     <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
   </si>
   <si>
+    <t>The stated low and high value are assumed to have arbitrarily high precision when it comes to determining which values are in the range. I.e. 1.99 is not in the range 2 -&gt; 3.</t>
+  </si>
+  <si>
     <t>Some analytes vary greatly over age.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+rng-2:If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
   </si>
   <si>
     <t>Observation.referenceRange.text</t>
@@ -2551,18 +2582,18 @@
         <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>76</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2585,13 +2616,13 @@
         <v>84</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2642,7 +2673,7 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>74</v>
@@ -2651,18 +2682,18 @@
         <v>83</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2685,13 +2716,13 @@
         <v>76</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2742,7 +2773,7 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -2759,14 +2790,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2785,16 +2816,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2832,19 +2863,19 @@
         <v>76</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -2856,15 +2887,15 @@
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2890,13 +2921,13 @@
         <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2946,7 +2977,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -2958,15 +2989,15 @@
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2989,16 +3020,16 @@
         <v>84</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3048,7 +3079,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -3060,15 +3091,15 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3091,16 +3122,16 @@
         <v>84</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3150,7 +3181,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -3162,15 +3193,15 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3193,16 +3224,16 @@
         <v>84</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3252,7 +3283,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -3264,15 +3295,15 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3295,16 +3326,16 @@
         <v>84</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3330,13 +3361,13 @@
         <v>76</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>76</v>
@@ -3354,7 +3385,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -3366,15 +3397,15 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3397,16 +3428,16 @@
         <v>84</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3432,13 +3463,13 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -3456,7 +3487,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -3468,15 +3499,15 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3499,16 +3530,16 @@
         <v>84</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3558,7 +3589,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -3567,18 +3598,18 @@
         <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3601,16 +3632,16 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3636,13 +3667,13 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -3660,7 +3691,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -3669,22 +3700,22 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3703,16 +3734,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3762,7 +3793,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -3771,22 +3802,22 @@
         <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3805,16 +3836,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3864,7 +3895,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3881,14 +3912,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3907,16 +3938,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3954,19 +3985,19 @@
         <v>76</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3975,22 +4006,22 @@
         <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4009,19 +4040,19 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -4058,19 +4089,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -4079,18 +4110,18 @@
         <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4113,17 +4144,17 @@
         <v>84</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -4172,7 +4203,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -4181,22 +4212,22 @@
         <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4215,17 +4246,19 @@
         <v>84</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -4274,7 +4307,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -4283,22 +4316,22 @@
         <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4317,16 +4350,16 @@
         <v>84</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4376,7 +4409,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -4385,18 +4418,18 @@
         <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4419,19 +4452,19 @@
         <v>84</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>10</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -4456,13 +4489,13 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>76</v>
@@ -4480,7 +4513,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -4489,18 +4522,18 @@
         <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4523,19 +4556,19 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4560,29 +4593,29 @@
         <v>76</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -4591,21 +4624,21 @@
         <v>75</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>76</v>
@@ -4627,19 +4660,19 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4649,7 +4682,7 @@
         <v>76</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>76</v>
@@ -4664,13 +4697,13 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4688,7 +4721,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -4697,22 +4730,22 @@
         <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4731,19 +4764,19 @@
         <v>84</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>63</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4768,13 +4801,13 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>76</v>
@@ -4792,7 +4825,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -4801,18 +4834,18 @@
         <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4835,13 +4868,13 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4892,7 +4925,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4909,14 +4942,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4935,16 +4968,16 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4982,19 +5015,19 @@
         <v>76</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -5003,18 +5036,18 @@
         <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5037,19 +5070,19 @@
         <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -5086,17 +5119,17 @@
         <v>76</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -5105,18 +5138,18 @@
         <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5139,13 +5172,13 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5196,7 +5229,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -5213,14 +5246,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5239,16 +5272,16 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5286,19 +5319,19 @@
         <v>76</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -5307,18 +5340,18 @@
         <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5341,19 +5374,19 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5402,7 +5435,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -5411,18 +5444,18 @@
         <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5445,16 +5478,16 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5504,7 +5537,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -5513,18 +5546,18 @@
         <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5547,17 +5580,19 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -5606,7 +5641,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -5615,18 +5650,18 @@
         <v>83</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5649,17 +5684,19 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5708,7 +5745,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5717,18 +5754,18 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5751,19 +5788,19 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5812,7 +5849,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5821,21 +5858,21 @@
         <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>76</v>
@@ -5857,19 +5894,19 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -5879,7 +5916,7 @@
         <v>76</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>76</v>
@@ -5918,7 +5955,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5927,18 +5964,18 @@
         <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5961,13 +5998,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6018,7 +6055,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -6035,14 +6072,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6061,16 +6098,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6108,19 +6145,19 @@
         <v>76</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -6129,18 +6166,18 @@
         <v>75</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6163,19 +6200,19 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -6224,7 +6261,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -6233,18 +6270,18 @@
         <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6267,16 +6304,16 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6326,7 +6363,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -6335,18 +6372,18 @@
         <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6369,17 +6406,19 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -6428,7 +6467,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -6437,18 +6476,18 @@
         <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6471,17 +6510,19 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6530,7 +6571,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6539,18 +6580,18 @@
         <v>83</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6573,19 +6614,19 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6634,7 +6675,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -6643,21 +6684,21 @@
         <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>76</v>
@@ -6679,19 +6720,19 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -6701,7 +6742,7 @@
         <v>76</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>76</v>
@@ -6716,11 +6757,11 @@
         <v>76</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>76</v>
@@ -6738,7 +6779,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -6747,18 +6788,18 @@
         <v>75</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6781,13 +6822,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6838,7 +6879,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6855,14 +6896,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6881,16 +6922,16 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6928,19 +6969,19 @@
         <v>76</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6949,18 +6990,18 @@
         <v>75</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6983,19 +7024,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -7044,7 +7085,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -7053,18 +7094,18 @@
         <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7087,16 +7128,16 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7146,7 +7187,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -7155,18 +7196,18 @@
         <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7189,17 +7230,19 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -7248,7 +7291,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -7257,18 +7300,18 @@
         <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7291,17 +7334,19 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -7350,7 +7395,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -7359,18 +7404,18 @@
         <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7393,19 +7438,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>76</v>
@@ -7454,7 +7499,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -7463,18 +7508,18 @@
         <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7497,19 +7542,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7558,7 +7603,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7567,18 +7612,18 @@
         <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7601,19 +7646,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7662,7 +7707,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7671,18 +7716,18 @@
         <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7705,16 +7750,16 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7764,7 +7809,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
@@ -7773,22 +7818,22 @@
         <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7807,19 +7852,19 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7868,7 +7913,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7877,22 +7922,22 @@
         <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7911,19 +7956,19 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -7972,7 +8017,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7981,18 +8026,18 @@
         <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8015,16 +8060,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8074,7 +8119,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -8083,18 +8128,18 @@
         <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8117,17 +8162,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8176,7 +8223,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -8185,18 +8232,18 @@
         <v>75</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8219,19 +8266,19 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8268,17 +8315,17 @@
         <v>76</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -8287,21 +8334,21 @@
         <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>76</v>
@@ -8323,19 +8370,19 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8345,7 +8392,7 @@
         <v>76</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>76</v>
@@ -8384,7 +8431,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -8393,18 +8440,18 @@
         <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8427,13 +8474,13 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8484,7 +8531,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
@@ -8501,14 +8548,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8527,16 +8574,16 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8574,19 +8621,19 @@
         <v>76</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -8595,18 +8642,18 @@
         <v>75</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8629,19 +8676,19 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8690,7 +8737,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
@@ -8699,18 +8746,18 @@
         <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8733,23 +8780,25 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q64" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="R64" t="s" s="2">
         <v>76</v>
@@ -8770,13 +8819,13 @@
         <v>76</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>76</v>
@@ -8794,7 +8843,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
@@ -8803,18 +8852,18 @@
         <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8837,17 +8886,19 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>76</v>
@@ -8896,7 +8947,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -8905,18 +8956,18 @@
         <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8939,17 +8990,19 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -8959,7 +9012,7 @@
         <v>76</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>76</v>
@@ -8998,7 +9051,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -9007,18 +9060,18 @@
         <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9041,19 +9094,19 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>76</v>
@@ -9078,11 +9131,11 @@
         <v>76</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>76</v>
@@ -9100,7 +9153,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -9109,18 +9162,18 @@
         <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9143,19 +9196,19 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9180,32 +9233,32 @@
         <v>76</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
       </c>
@@ -9213,22 +9266,22 @@
         <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9247,19 +9300,19 @@
         <v>76</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>76</v>
@@ -9284,13 +9337,13 @@
         <v>76</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>76</v>
@@ -9308,7 +9361,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
@@ -9317,18 +9370,18 @@
         <v>75</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9351,19 +9404,19 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>76</v>
@@ -9412,7 +9465,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>74</v>
@@ -9421,18 +9474,18 @@
         <v>75</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9455,16 +9508,16 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9490,32 +9543,32 @@
         <v>76</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="Z71" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AA71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="AG71" t="s" s="2">
         <v>74</v>
       </c>
@@ -9523,18 +9576,18 @@
         <v>83</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9557,19 +9610,19 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>76</v>
@@ -9594,32 +9647,32 @@
         <v>76</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AG72" t="s" s="2">
         <v>74</v>
       </c>
@@ -9627,18 +9680,18 @@
         <v>83</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9661,16 +9714,16 @@
         <v>76</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9720,7 +9773,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
@@ -9729,18 +9782,18 @@
         <v>83</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9763,16 +9816,16 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9822,7 +9875,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
@@ -9831,18 +9884,18 @@
         <v>83</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9865,19 +9918,19 @@
         <v>76</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>76</v>
@@ -9926,7 +9979,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
@@ -9935,18 +9988,18 @@
         <v>75</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9969,13 +10022,13 @@
         <v>76</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10026,7 +10079,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
@@ -10043,14 +10096,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10069,16 +10122,16 @@
         <v>76</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10116,19 +10169,19 @@
         <v>76</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
@@ -10137,22 +10190,22 @@
         <v>75</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10171,19 +10224,19 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>76</v>
@@ -10232,7 +10285,7 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>74</v>
@@ -10241,18 +10294,18 @@
         <v>75</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10275,15 +10328,17 @@
         <v>76</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>76</v>
@@ -10332,7 +10387,7 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>74</v>
@@ -10341,18 +10396,18 @@
         <v>83</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>95</v>
+        <v>460</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10375,15 +10430,17 @@
         <v>76</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>76</v>
@@ -10432,7 +10489,7 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>74</v>
@@ -10441,18 +10498,18 @@
         <v>83</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>95</v>
+        <v>460</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10475,19 +10532,19 @@
         <v>76</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>76</v>
@@ -10512,13 +10569,13 @@
         <v>76</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>76</v>
@@ -10536,7 +10593,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
@@ -10545,18 +10602,18 @@
         <v>83</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10579,19 +10636,19 @@
         <v>76</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>76</v>
@@ -10616,13 +10673,13 @@
         <v>76</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>76</v>
@@ -10640,7 +10697,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>74</v>
@@ -10649,18 +10706,18 @@
         <v>75</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10683,17 +10740,19 @@
         <v>76</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="O83" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>76</v>
@@ -10742,7 +10801,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
@@ -10751,18 +10810,18 @@
         <v>83</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>95</v>
+        <v>484</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10785,15 +10844,17 @@
         <v>76</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>76</v>
@@ -10842,7 +10903,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -10851,18 +10912,18 @@
         <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10885,16 +10946,16 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10944,7 +11005,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -10953,18 +11014,18 @@
         <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10987,16 +11048,16 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11046,7 +11107,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -11055,18 +11116,18 @@
         <v>75</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11089,19 +11150,19 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>76</v>
@@ -11138,17 +11199,17 @@
         <v>76</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -11157,18 +11218,18 @@
         <v>75</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11191,13 +11252,13 @@
         <v>76</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11248,7 +11309,7 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>74</v>
@@ -11265,14 +11326,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11291,16 +11352,16 @@
         <v>76</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11338,19 +11399,19 @@
         <v>76</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
@@ -11359,22 +11420,22 @@
         <v>75</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11393,19 +11454,19 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>76</v>
@@ -11454,7 +11515,7 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>74</v>
@@ -11463,18 +11524,18 @@
         <v>75</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11497,19 +11558,19 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>76</v>
@@ -11534,13 +11595,13 @@
         <v>76</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>76</v>
@@ -11558,7 +11619,7 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -11567,18 +11628,18 @@
         <v>83</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11601,19 +11662,19 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>76</v>
@@ -11650,17 +11711,17 @@
         <v>76</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AC92" s="2"/>
       <c r="AD92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
@@ -11669,21 +11730,21 @@
         <v>83</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>76</v>
@@ -11705,19 +11766,19 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>76</v>
@@ -11766,7 +11827,7 @@
         <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
@@ -11775,18 +11836,18 @@
         <v>83</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11809,13 +11870,13 @@
         <v>76</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11866,7 +11927,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>74</v>
@@ -11883,14 +11944,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -11909,16 +11970,16 @@
         <v>76</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11956,19 +12017,19 @@
         <v>76</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
@@ -11977,18 +12038,18 @@
         <v>75</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12011,19 +12072,19 @@
         <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>76</v>
@@ -12072,7 +12133,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
@@ -12081,18 +12142,18 @@
         <v>83</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12115,23 +12176,25 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O97" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q97" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="R97" t="s" s="2">
         <v>76</v>
@@ -12152,13 +12215,13 @@
         <v>76</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>76</v>
@@ -12176,7 +12239,7 @@
         <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -12185,18 +12248,18 @@
         <v>83</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12219,17 +12282,19 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O98" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>76</v>
@@ -12278,7 +12343,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
@@ -12287,18 +12352,18 @@
         <v>83</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12321,17 +12386,19 @@
         <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="O99" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>76</v>
@@ -12341,7 +12408,7 @@
         <v>76</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>76</v>
@@ -12380,7 +12447,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>74</v>
@@ -12389,18 +12456,18 @@
         <v>83</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12423,19 +12490,19 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>76</v>
@@ -12484,7 +12551,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
@@ -12493,18 +12560,18 @@
         <v>83</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12527,19 +12594,19 @@
         <v>76</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>76</v>
@@ -12564,13 +12631,13 @@
         <v>76</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>76</v>
@@ -12588,7 +12655,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
@@ -12597,22 +12664,22 @@
         <v>83</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -12631,19 +12698,19 @@
         <v>76</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>76</v>
@@ -12668,13 +12735,13 @@
         <v>76</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>76</v>
@@ -12692,7 +12759,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
@@ -12701,18 +12768,18 @@
         <v>75</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12738,16 +12805,16 @@
         <v>77</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>76</v>
@@ -12796,7 +12863,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -12808,18 +12875,18 @@
         <v>76</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>76</v>
@@ -12841,19 +12908,19 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>76</v>
@@ -12902,7 +12969,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
@@ -12911,18 +12978,18 @@
         <v>75</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12945,13 +13012,13 @@
         <v>76</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13002,7 +13069,7 @@
         <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>74</v>
@@ -13019,14 +13086,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13045,16 +13112,16 @@
         <v>76</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13092,19 +13159,19 @@
         <v>76</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
@@ -13113,22 +13180,22 @@
         <v>75</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13147,19 +13214,19 @@
         <v>84</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>76</v>
@@ -13208,7 +13275,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
@@ -13217,18 +13284,18 @@
         <v>75</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13251,19 +13318,19 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>76</v>
@@ -13288,13 +13355,13 @@
         <v>76</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>76</v>
@@ -13312,7 +13379,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>83</v>
@@ -13321,18 +13388,18 @@
         <v>83</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13355,13 +13422,13 @@
         <v>76</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -13412,7 +13479,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>74</v>
@@ -13429,14 +13496,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -13455,16 +13522,16 @@
         <v>76</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13502,19 +13569,19 @@
         <v>76</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>74</v>
@@ -13526,15 +13593,15 @@
         <v>76</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13557,19 +13624,19 @@
         <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>76</v>
@@ -13606,17 +13673,17 @@
         <v>76</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="AC111" s="2"/>
       <c r="AD111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
@@ -13628,18 +13695,18 @@
         <v>76</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>76</v>
@@ -13661,19 +13728,19 @@
         <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>76</v>
@@ -13698,11 +13765,11 @@
         <v>76</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>76</v>
@@ -13720,7 +13787,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -13732,18 +13799,18 @@
         <v>76</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>76</v>
@@ -13765,19 +13832,19 @@
         <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>76</v>
@@ -13802,11 +13869,11 @@
         <v>76</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>76</v>
@@ -13824,7 +13891,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
@@ -13836,15 +13903,15 @@
         <v>76</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13867,19 +13934,19 @@
         <v>84</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -13928,7 +13995,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
@@ -13940,15 +14007,15 @@
         <v>76</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13971,19 +14038,19 @@
         <v>84</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>76</v>
@@ -14020,17 +14087,17 @@
         <v>76</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AC115" s="2"/>
       <c r="AD115" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
@@ -14039,21 +14106,21 @@
         <v>83</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>76</v>
@@ -14075,19 +14142,19 @@
         <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>76</v>
@@ -14136,7 +14203,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -14145,18 +14212,18 @@
         <v>83</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14179,13 +14246,13 @@
         <v>76</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14236,7 +14303,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -14253,14 +14320,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -14279,16 +14346,16 @@
         <v>76</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -14326,19 +14393,19 @@
         <v>76</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
@@ -14347,18 +14414,18 @@
         <v>75</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14381,19 +14448,19 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>76</v>
@@ -14442,7 +14509,7 @@
         <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
@@ -14451,18 +14518,18 @@
         <v>83</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14485,23 +14552,25 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O120" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q120" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="R120" t="s" s="2">
         <v>76</v>
@@ -14522,13 +14591,13 @@
         <v>76</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>76</v>
@@ -14546,7 +14615,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>74</v>
@@ -14555,18 +14624,18 @@
         <v>83</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14589,17 +14658,19 @@
         <v>84</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O121" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>76</v>
@@ -14609,7 +14680,7 @@
         <v>76</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>76</v>
@@ -14648,7 +14719,7 @@
         <v>76</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>74</v>
@@ -14657,18 +14728,18 @@
         <v>83</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14691,17 +14762,19 @@
         <v>84</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N122" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="O122" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>76</v>
@@ -14711,7 +14784,7 @@
         <v>76</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>76</v>
@@ -14750,7 +14823,7 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
@@ -14759,18 +14832,18 @@
         <v>83</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14793,19 +14866,19 @@
         <v>84</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>76</v>
@@ -14815,7 +14888,7 @@
         <v>76</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>76</v>
@@ -14854,7 +14927,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
@@ -14863,18 +14936,18 @@
         <v>83</v>
       </c>
       <c r="AI123" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14897,19 +14970,19 @@
         <v>76</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>76</v>
@@ -14934,13 +15007,13 @@
         <v>76</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>76</v>
@@ -14958,7 +15031,7 @@
         <v>76</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
@@ -14967,22 +15040,22 @@
         <v>83</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -15001,19 +15074,19 @@
         <v>76</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>76</v>
@@ -15038,13 +15111,13 @@
         <v>76</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>76</v>
@@ -15062,7 +15135,7 @@
         <v>76</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
@@ -15071,18 +15144,18 @@
         <v>75</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15108,16 +15181,16 @@
         <v>77</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>76</v>
@@ -15166,7 +15239,7 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
@@ -15178,18 +15251,18 @@
         <v>76</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>76</v>
@@ -15211,19 +15284,19 @@
         <v>84</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>76</v>
@@ -15272,7 +15345,7 @@
         <v>76</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>74</v>
@@ -15281,18 +15354,18 @@
         <v>75</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15315,13 +15388,13 @@
         <v>76</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -15372,7 +15445,7 @@
         <v>76</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>74</v>
@@ -15389,14 +15462,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -15415,16 +15488,16 @@
         <v>76</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -15462,19 +15535,19 @@
         <v>76</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="AC129" t="s" s="2">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="AD129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
@@ -15483,22 +15556,22 @@
         <v>75</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -15517,19 +15590,19 @@
         <v>84</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>76</v>
@@ -15578,7 +15651,7 @@
         <v>76</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
@@ -15587,18 +15660,18 @@
         <v>75</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15621,19 +15694,19 @@
         <v>84</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>76</v>
@@ -15658,13 +15731,13 @@
         <v>76</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>76</v>
@@ -15682,7 +15755,7 @@
         <v>76</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>83</v>
@@ -15691,18 +15764,18 @@
         <v>83</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15725,13 +15798,13 @@
         <v>76</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -15782,7 +15855,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
@@ -15799,14 +15872,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -15825,16 +15898,16 @@
         <v>76</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -15872,19 +15945,19 @@
         <v>76</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>74</v>
@@ -15896,15 +15969,15 @@
         <v>76</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15927,19 +16000,19 @@
         <v>84</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>76</v>
@@ -15976,17 +16049,17 @@
         <v>76</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="AC134" s="2"/>
       <c r="AD134" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
@@ -15998,18 +16071,18 @@
         <v>76</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>76</v>
@@ -16031,19 +16104,19 @@
         <v>84</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
@@ -16068,11 +16141,11 @@
         <v>76</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>76</v>
@@ -16090,7 +16163,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
@@ -16102,18 +16175,18 @@
         <v>76</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>76</v>
@@ -16135,19 +16208,19 @@
         <v>84</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>76</v>
@@ -16172,11 +16245,11 @@
         <v>76</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>76</v>
@@ -16194,7 +16267,7 @@
         <v>76</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
@@ -16206,15 +16279,15 @@
         <v>76</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16237,19 +16310,19 @@
         <v>84</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>76</v>
@@ -16298,7 +16371,7 @@
         <v>76</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>74</v>
@@ -16310,15 +16383,15 @@
         <v>76</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16341,19 +16414,19 @@
         <v>84</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>76</v>
@@ -16390,17 +16463,17 @@
         <v>76</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AC138" s="2"/>
       <c r="AD138" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>74</v>
@@ -16409,21 +16482,21 @@
         <v>83</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>76</v>
@@ -16445,19 +16518,19 @@
         <v>84</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>76</v>
@@ -16506,7 +16579,7 @@
         <v>76</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>74</v>
@@ -16515,18 +16588,18 @@
         <v>83</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16549,13 +16622,13 @@
         <v>76</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -16606,7 +16679,7 @@
         <v>76</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>74</v>
@@ -16623,14 +16696,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -16649,16 +16722,16 @@
         <v>76</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -16696,19 +16769,19 @@
         <v>76</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>74</v>
@@ -16717,18 +16790,18 @@
         <v>75</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16751,19 +16824,19 @@
         <v>84</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>76</v>
@@ -16812,7 +16885,7 @@
         <v>76</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>74</v>
@@ -16821,18 +16894,18 @@
         <v>83</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16855,23 +16928,25 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O143" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q143" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="R143" t="s" s="2">
         <v>76</v>
@@ -16892,13 +16967,13 @@
         <v>76</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>76</v>
@@ -16916,7 +16991,7 @@
         <v>76</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>74</v>
@@ -16925,18 +17000,18 @@
         <v>83</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16959,17 +17034,19 @@
         <v>84</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N144" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O144" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>76</v>
@@ -16979,7 +17056,7 @@
         <v>76</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>76</v>
@@ -17018,7 +17095,7 @@
         <v>76</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>74</v>
@@ -17027,18 +17104,18 @@
         <v>83</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17061,17 +17138,19 @@
         <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N145" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="O145" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>76</v>
@@ -17081,7 +17160,7 @@
         <v>76</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>76</v>
@@ -17120,7 +17199,7 @@
         <v>76</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>74</v>
@@ -17129,18 +17208,18 @@
         <v>83</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17163,19 +17242,19 @@
         <v>84</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>76</v>
@@ -17185,7 +17264,7 @@
         <v>76</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>76</v>
@@ -17224,7 +17303,7 @@
         <v>76</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>74</v>
@@ -17233,18 +17312,18 @@
         <v>83</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17267,19 +17346,19 @@
         <v>76</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>76</v>
@@ -17304,13 +17383,13 @@
         <v>76</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>76</v>
@@ -17328,7 +17407,7 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
@@ -17337,22 +17416,22 @@
         <v>83</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -17371,19 +17450,19 @@
         <v>76</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>76</v>
@@ -17408,13 +17487,13 @@
         <v>76</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>76</v>
@@ -17432,7 +17511,7 @@
         <v>76</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>74</v>
@@ -17441,18 +17520,18 @@
         <v>75</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17478,16 +17557,16 @@
         <v>77</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>76</v>
@@ -17536,7 +17615,7 @@
         <v>76</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>74</v>
@@ -17548,7 +17627,7 @@
         <v>76</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-bf.xlsx
+++ b/branches/release/v2027.0.0-ballot/StructureDefinition-mii-pr-lungenfunktion-bf.xlsx
@@ -922,7 +922,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="271625008"/&gt;
   &lt;display value="Rate of spontaneous respiration (observable entity)"/&gt;
 &lt;/valueCoding&gt;</t>
